--- a/data/trans_bre/P5B_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P5B_R-Provincia-trans_bre.xlsx
@@ -602,7 +602,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>-2,38</t>
+          <t>-2,3</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -637,7 +637,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-37,7%</t>
+          <t>-36,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -660,17 +660,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,08; 10,33</t>
+          <t>1,09; 10,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-11,36; 6,16</t>
+          <t>-12,32; 6,09</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-13,61; -0,8</t>
+          <t>-14,13; -0,59</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -702,7 +702,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 8,04</t>
+          <t>-1,72; 8,32</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-7,26; 5,69</t>
+          <t>-7,25; 6,62</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 8,05</t>
+          <t>-0,05; 7,8</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,77; 61,18</t>
+          <t>0,8; 63,99</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-83,57; 259,75</t>
+          <t>-85,36; 362,76</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -802,7 +802,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,02; 7,34</t>
+          <t>-5,23; 7,61</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,24</t>
+          <t>0,0; 9,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -875,12 +875,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 4,05</t>
+          <t>-4,59; 3,8</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-71,23; 386,52</t>
+          <t>-80,73; 390,72</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1,53</t>
+          <t>1,58</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-7,45; 1,01</t>
+          <t>-7,57; 1,05</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,12</t>
+          <t>0,0; 10,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 8,39</t>
+          <t>-3,27; 8,11</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-11,99; -1,35</t>
+          <t>-10,92; -1,17</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,17; 50,59</t>
+          <t>-5,16; 44,8</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-15,93; 8,1</t>
+          <t>-15,96; 7,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 6,18</t>
+          <t>-3,48; 7,65</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,26; 0,0</t>
+          <t>-6,34; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1102,7 +1102,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,74</t>
+          <t>0,0; 9,35</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,54</t>
+          <t>0,0; 7,58</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2,13</t>
+          <t>2,14</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-0,59</t>
+          <t>-0,6</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>392,18%</t>
+          <t>394,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-36,95%</t>
+          <t>-37,33%</t>
         </is>
       </c>
     </row>
@@ -1260,27 +1260,27 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,6; 3,53</t>
+          <t>-4,59; 4,07</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 3,16</t>
+          <t>-1,04; 3,41</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 5,13</t>
+          <t>-0,04; 5,42</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 1,52</t>
+          <t>-3,41; 1,53</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-77,97; 198,62</t>
+          <t>-77,96; 179,73</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0,66</t>
+          <t>0,67</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1360,27 +1360,27 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 4,75</t>
+          <t>-3,52; 5,04</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,33</t>
+          <t>0,0; 3,13</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,96</t>
+          <t>0,0; 2,48</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 0,0</t>
+          <t>-3,2; 0,0</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-77,66; 401,21</t>
+          <t>-73,63; 373,82</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1437,17 +1437,17 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>61,45%</t>
+          <t>62,01%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>267,31%</t>
+          <t>266,94%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 2,88</t>
+          <t>-0,86; 2,8</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 1,69</t>
+          <t>-0,84; 1,86</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 1,83</t>
+          <t>-0,44; 1,83</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 18,1</t>
+          <t>-0,93; 14,85</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-24,52; 132,85</t>
+          <t>-24,23; 123,67</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-51,07; 158,5</t>
+          <t>-43,07; 200,01</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-35,68; 289,72</t>
+          <t>-27,02; 274,41</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-63,98; 1757,94</t>
+          <t>-65,67; 2583,94</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P5B_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P5B_R-Provincia-trans_bre.xlsx
@@ -660,17 +660,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,09; 10,6</t>
+          <t>1,08; 10,45</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-12,32; 6,09</t>
+          <t>-12,28; 5,81</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-14,13; -0,59</t>
+          <t>-15,13; -0,99</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 8,32</t>
+          <t>-1,84; 8,15</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-7,25; 6,62</t>
+          <t>-6,5; 7,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 7,8</t>
+          <t>-0,06; 7,85</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,8; 63,99</t>
+          <t>0,79; 65,34</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-85,36; 362,76</t>
+          <t>-81,2; 362,74</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,23; 7,61</t>
+          <t>-4,79; 7,83</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,27</t>
+          <t>0,0; 10,29</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -875,12 +875,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 3,8</t>
+          <t>-4,71; 3,51</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-80,73; 390,72</t>
+          <t>-72,5; 440,41</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-7,57; 1,05</t>
+          <t>-7,03; 1,7</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,44</t>
+          <t>0,0; 10,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 8,11</t>
+          <t>-3,23; 7,94</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-10,92; -1,17</t>
+          <t>-11,76; -1,2</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,16; 44,8</t>
+          <t>-5,36; 43,89</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-15,96; 7,0</t>
+          <t>-14,87; 9,83</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 7,65</t>
+          <t>-3,55; 6,91</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,34; 0,0</t>
+          <t>-6,99; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,35</t>
+          <t>0,0; 8,11</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,58</t>
+          <t>0,0; 6,8</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1260,27 +1260,27 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 4,07</t>
+          <t>-4,47; 4,09</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 3,41</t>
+          <t>-1,01; 3,32</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 5,42</t>
+          <t>-0,0; 5,07</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 1,53</t>
+          <t>-3,05; 1,48</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-77,96; 179,73</t>
+          <t>-72,67; 227,14</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1360,27 +1360,27 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 5,04</t>
+          <t>-3,35; 4,97</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,13</t>
+          <t>0,0; 3,36</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,48</t>
+          <t>0,0; 3,1</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 0,0</t>
+          <t>-3,17; 0,0</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-73,63; 373,82</t>
+          <t>-71,71; 458,37</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 2,8</t>
+          <t>-0,91; 2,8</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 1,86</t>
+          <t>-0,95; 1,84</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 1,83</t>
+          <t>-0,41; 1,97</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 14,85</t>
+          <t>-0,92; 17,02</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-24,23; 123,67</t>
+          <t>-25,29; 118,67</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-43,07; 200,01</t>
+          <t>-45,73; 217,33</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-27,02; 274,41</t>
+          <t>-29,29; 319,89</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-65,67; 2583,94</t>
+          <t>-63,75; 3077,27</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P5B_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P5B_R-Provincia-trans_bre.xlsx
@@ -660,17 +660,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,08; 10,45</t>
+          <t>1,08; 10,33</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-12,28; 5,81</t>
+          <t>-11,8; 6,16</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-15,13; -0,99</t>
+          <t>-13,61; -0,8</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>22,11</t>
+          <t>4,07</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 8,15</t>
+          <t>-1,69; 8,04</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,5; 7,17</t>
+          <t>-7,26; 5,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 7,85</t>
+          <t>-0,02; 8,05</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,79; 65,34</t>
+          <t>0,7; 15,38</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-81,2; 362,74</t>
+          <t>-83,57; 259,75</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-22,76%</t>
+          <t>-23,26%</t>
         </is>
       </c>
     </row>
@@ -860,12 +860,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,79; 7,83</t>
+          <t>-5,02; 7,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,29</t>
+          <t>0,0; 7,24</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -875,12 +875,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,71; 3,51</t>
+          <t>-4,23; 4,07</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-72,5; 440,41</t>
+          <t>-71,23; 386,52</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-4,46</t>
+          <t>-4,76</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-7,03; 1,7</t>
+          <t>-7,45; 1,01</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,41</t>
+          <t>0,0; 9,12</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 7,94</t>
+          <t>-3,28; 8,44</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-11,76; -1,2</t>
+          <t>-13,53; -1,52</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-1,19</t>
+          <t>-1,22</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,36; 43,89</t>
+          <t>-5,17; 50,59</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-14,87; 9,83</t>
+          <t>-15,93; 8,1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 6,91</t>
+          <t>-3,52; 6,18</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,99; 0,0</t>
+          <t>-6,4; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1,32</t>
+          <t>1,35</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,11</t>
+          <t>0,0; 6,74</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,8</t>
+          <t>0,0; 6,65</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-0,6</t>
+          <t>-0,56</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-37,33%</t>
+          <t>-33,41%</t>
         </is>
       </c>
     </row>
@@ -1260,27 +1260,27 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,47; 4,09</t>
+          <t>-4,6; 3,53</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 3,32</t>
+          <t>-0,56; 3,16</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,0; 5,07</t>
+          <t>0,0; 5,3</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 1,48</t>
+          <t>-3,36; 1,75</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-72,67; 227,14</t>
+          <t>-77,97; 198,62</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-0,96</t>
+          <t>-0,91</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 4,97</t>
+          <t>-3,78; 4,75</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1370,17 +1370,17 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,1</t>
+          <t>0,0; 2,96</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 0,0</t>
+          <t>-3,1; 0,0</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-71,71; 458,37</t>
+          <t>-77,66; 401,21</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3,42</t>
+          <t>-0,17</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>266,94%</t>
+          <t>-13,03%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 2,8</t>
+          <t>-0,96; 2,88</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 1,84</t>
+          <t>-0,84; 1,89</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 1,97</t>
+          <t>-0,49; 1,84</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 17,02</t>
+          <t>-1,19; 1,43</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-25,29; 118,67</t>
+          <t>-24,52; 132,85</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-45,73; 217,33</t>
+          <t>-43,94; 193,67</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-29,29; 319,89</t>
+          <t>-36,16; 275,88</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-63,75; 3077,27</t>
+          <t>-67,5; 204,05</t>
         </is>
       </c>
     </row>
